--- a/03_Group_comparisons/Proteome_clusters/c_data/07_cluster_phenotype.xlsx
+++ b/03_Group_comparisons/Proteome_clusters/c_data/07_cluster_phenotype.xlsx
@@ -243,7 +243,7 @@
     <t>02_Groups/Proteome_T1/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>73de93985bcf7846355f2fe1f949411c</t>
+    <t>678cf7da1ad5c67fcbedb72ed9fd0af0</t>
   </si>
   <si>
     <t>clusters_T2</t>
@@ -252,7 +252,7 @@
     <t>02_Groups/Proteome_T2/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>f4dabcec04bf30833e381b0858deefc2</t>
+    <t>24ce0b5aee6a397d70072cc1047b09c4</t>
   </si>
   <si>
     <t>clusters_T3</t>
@@ -261,7 +261,7 @@
     <t>02_Groups/Proteome_T3/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>4c0b5ae6b12d629b21ee879e58644cd8</t>
+    <t>895c47d84d879986f97994cce61f3ceb</t>
   </si>
   <si>
     <t>clusters_training</t>
@@ -270,7 +270,7 @@
     <t>02_Groups/Proteome_training/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>8875e30f69b9b331f48fd6e602a79386</t>
+    <t>3852297d398ef9a604a3b17e910831e3</t>
   </si>
   <si>
     <t>clusters_acute</t>
@@ -279,7 +279,7 @@
     <t>02_Groups/Proteome_acute/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>d80f6cb54482b3e0167044b56804f223</t>
+    <t>88f1830b45c8bd84a3abb358f54e130c</t>
   </si>
   <si>
     <t>phenotype</t>
@@ -288,7 +288,7 @@
     <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
-    <t>5a1989db406daa0b70189a9f0df52cf3</t>
+    <t>cdb8d908fb24ab0d2be6f2d00021db81</t>
   </si>
   <si>
     <t>BiocGenerics</t>
